--- a/backend/test_trading_export.xlsx
+++ b/backend/test_trading_export.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,13 +50,24 @@
       <color rgb="002F5597"/>
       <sz val="16"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -71,12 +82,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,7 +469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2025-12-15 07:23:25 UTC</t>
+          <t>Generated: 2026-02-24 11:49:24 UTC</t>
         </is>
       </c>
     </row>
@@ -543,8 +557,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -554,11 +579,117 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trades analysis will be implemented based on available trades data.</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Trade ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Order ID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Position ID</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>trade_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pos_1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trade_2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pos_2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -574,8 +705,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
@@ -585,9 +727,123 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Orders analysis will be implemented based on available orders data.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Order ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Position ID</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Filled Qty</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Avg Fill Price</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Created At</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>order_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pos_1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2024-01-15T10:30:00Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>order_2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pos_2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2024-01-16T11:15:00Z</t>
         </is>
       </c>
     </row>
